--- a/master/Training_Database_Master.xlsx
+++ b/master/Training_Database_Master.xlsx
@@ -2978,54 +2978,135 @@
     </row>
     <row r="16" ht="15.75" customHeight="1" s="90">
       <c r="A16" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B16" s="17" t="n"/>
-      <c r="C16" s="11" t="n"/>
-      <c r="D16" s="11" t="n"/>
-      <c r="E16" s="11" t="n"/>
-      <c r="F16" s="11" t="n"/>
-      <c r="G16" s="11" t="n"/>
+        <v>2</v>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>BOSHSO1</t>
+        </is>
+      </c>
+      <c r="C16" s="11" t="inlineStr">
+        <is>
+          <t>November 2 - 5, 2025</t>
+        </is>
+      </c>
+      <c r="D16" s="11" t="inlineStr">
+        <is>
+          <t>#701c</t>
+        </is>
+      </c>
+      <c r="E16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F16" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G16" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="n"/>
+      <c r="M16" s="11" t="inlineStr">
+        <is>
+          <t>Public - Online</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-11-25 15:17:12</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="90">
       <c r="A17" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B17" s="17" t="n"/>
-      <c r="C17" s="11" t="n"/>
-      <c r="D17" s="11" t="n"/>
-      <c r="E17" s="11" t="n"/>
-      <c r="F17" s="11" t="n"/>
-      <c r="G17" s="11" t="n"/>
+        <v>3</v>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>BOSHSO1</t>
+        </is>
+      </c>
+      <c r="C17" s="11" t="inlineStr">
+        <is>
+          <t>November 2 - 5, 2025</t>
+        </is>
+      </c>
+      <c r="D17" s="11" t="inlineStr">
+        <is>
+          <t>#701c</t>
+        </is>
+      </c>
+      <c r="E17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F17" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G17" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="n"/>
+      <c r="M17" s="11" t="inlineStr">
+        <is>
+          <t>Public - Online</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-11-25 15:18:20</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="90">
       <c r="A18" s="10" t="n">
-        <v>5</v>
-      </c>
-      <c r="B18" s="17" t="n"/>
-      <c r="C18" s="11" t="n"/>
-      <c r="D18" s="11" t="n"/>
-      <c r="E18" s="11" t="n"/>
-      <c r="F18" s="11" t="n"/>
-      <c r="G18" s="11" t="n"/>
+        <v>4</v>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>BOSHSO1</t>
+        </is>
+      </c>
+      <c r="C18" s="11" t="inlineStr">
+        <is>
+          <t>November 2 - 5, 2025</t>
+        </is>
+      </c>
+      <c r="D18" s="11" t="inlineStr">
+        <is>
+          <t>#701c</t>
+        </is>
+      </c>
+      <c r="E18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G18" s="11" t="n">
+        <v>0</v>
+      </c>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="n"/>
+      <c r="M18" s="11" t="inlineStr">
+        <is>
+          <t>Public - Online</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-11-25 15:23:27</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="90">
       <c r="A19" s="10" t="n">

--- a/master/Training_Database_Master.xlsx
+++ b/master/Training_Database_Master.xlsx
@@ -2889,224 +2889,79 @@
       <c r="M13" s="112" t="n"/>
     </row>
     <row r="14" ht="15.75" customFormat="1" customHeight="1" s="30">
-      <c r="A14" s="9" t="n">
-        <v>0</v>
-      </c>
-      <c r="B14" s="24" t="inlineStr">
-        <is>
-          <t>BOSHSO1</t>
-        </is>
-      </c>
-      <c r="C14" s="27" t="inlineStr">
-        <is>
-          <t>November 2 - 5, 2025</t>
-        </is>
-      </c>
-      <c r="D14" s="28" t="inlineStr">
-        <is>
-          <t>#701c</t>
-        </is>
-      </c>
-      <c r="E14" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="F14" s="28" t="n">
-        <v>1</v>
-      </c>
-      <c r="G14" s="28" t="n">
-        <v>0</v>
-      </c>
+      <c r="A14" s="9" t="n"/>
+      <c r="B14" s="24" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="28" t="n"/>
+      <c r="E14" s="28" t="n"/>
+      <c r="F14" s="28" t="n"/>
+      <c r="G14" s="28" t="n"/>
       <c r="H14" s="28" t="n"/>
       <c r="I14" s="28" t="n"/>
       <c r="J14" s="29" t="n"/>
       <c r="K14" s="25" t="n"/>
       <c r="L14" s="25" t="n"/>
-      <c r="M14" s="25" t="inlineStr">
-        <is>
-          <t>Public - Online</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-11-25 14:58:33</t>
-        </is>
-      </c>
+      <c r="M14" s="25" t="n"/>
     </row>
     <row r="15" ht="15.75" customHeight="1" s="90">
-      <c r="A15" s="10" t="n">
-        <v>1</v>
-      </c>
-      <c r="B15" s="24" t="inlineStr">
-        <is>
-          <t>BOSHSO1</t>
-        </is>
-      </c>
-      <c r="C15" s="27" t="inlineStr">
-        <is>
-          <t>October 26, 2025, October 29, 2025, November 7, 2025, November 9, 2025</t>
-        </is>
-      </c>
-      <c r="D15" s="25" t="inlineStr">
-        <is>
-          <t>#f4cf</t>
-        </is>
-      </c>
-      <c r="E15" s="25" t="n">
-        <v>11</v>
-      </c>
-      <c r="F15" s="25" t="n">
-        <v>8</v>
-      </c>
-      <c r="G15" s="25" t="n">
-        <v>3</v>
-      </c>
+      <c r="A15" s="10" t="n"/>
+      <c r="B15" s="24" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="25" t="n"/>
+      <c r="E15" s="25" t="n"/>
+      <c r="F15" s="25" t="n"/>
+      <c r="G15" s="25" t="n"/>
       <c r="H15" s="25" t="n"/>
       <c r="I15" s="28" t="n"/>
       <c r="J15" s="29" t="n"/>
       <c r="K15" s="25" t="n"/>
       <c r="L15" s="25" t="n"/>
-      <c r="M15" s="25" t="inlineStr">
-        <is>
-          <t>Public - Online</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-11-25 15:00:09</t>
-        </is>
-      </c>
+      <c r="M15" s="25" t="n"/>
     </row>
     <row r="16" ht="15.75" customHeight="1" s="90">
-      <c r="A16" s="10" t="n">
-        <v>2</v>
-      </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>BOSHSO1</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
-        <is>
-          <t>November 2 - 5, 2025</t>
-        </is>
-      </c>
-      <c r="D16" s="11" t="inlineStr">
-        <is>
-          <t>#701c</t>
-        </is>
-      </c>
-      <c r="E16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F16" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G16" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A16" s="10" t="n"/>
+      <c r="B16" s="17" t="n"/>
+      <c r="C16" s="11" t="n"/>
+      <c r="D16" s="11" t="n"/>
+      <c r="E16" s="11" t="n"/>
+      <c r="F16" s="11" t="n"/>
+      <c r="G16" s="11" t="n"/>
       <c r="H16" s="11" t="n"/>
       <c r="I16" s="11" t="n"/>
       <c r="J16" s="11" t="n"/>
       <c r="K16" s="11" t="n"/>
       <c r="L16" s="11" t="n"/>
-      <c r="M16" s="11" t="inlineStr">
-        <is>
-          <t>Public - Online</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-11-25 15:17:12</t>
-        </is>
-      </c>
+      <c r="M16" s="11" t="n"/>
     </row>
     <row r="17" ht="15.75" customHeight="1" s="90">
-      <c r="A17" s="10" t="n">
-        <v>3</v>
-      </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>BOSHSO1</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
-        <is>
-          <t>November 2 - 5, 2025</t>
-        </is>
-      </c>
-      <c r="D17" s="11" t="inlineStr">
-        <is>
-          <t>#701c</t>
-        </is>
-      </c>
-      <c r="E17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F17" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G17" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A17" s="10" t="n"/>
+      <c r="B17" s="17" t="n"/>
+      <c r="C17" s="11" t="n"/>
+      <c r="D17" s="11" t="n"/>
+      <c r="E17" s="11" t="n"/>
+      <c r="F17" s="11" t="n"/>
+      <c r="G17" s="11" t="n"/>
       <c r="H17" s="11" t="n"/>
       <c r="I17" s="11" t="n"/>
       <c r="J17" s="11" t="n"/>
       <c r="K17" s="11" t="n"/>
       <c r="L17" s="11" t="n"/>
-      <c r="M17" s="11" t="inlineStr">
-        <is>
-          <t>Public - Online</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-11-25 15:18:20</t>
-        </is>
-      </c>
+      <c r="M17" s="11" t="n"/>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="90">
-      <c r="A18" s="10" t="n">
-        <v>4</v>
-      </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>BOSHSO1</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
-        <is>
-          <t>November 2 - 5, 2025</t>
-        </is>
-      </c>
-      <c r="D18" s="11" t="inlineStr">
-        <is>
-          <t>#701c</t>
-        </is>
-      </c>
-      <c r="E18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F18" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G18" s="11" t="n">
-        <v>0</v>
-      </c>
+      <c r="A18" s="10" t="n"/>
+      <c r="B18" s="17" t="n"/>
+      <c r="C18" s="11" t="n"/>
+      <c r="D18" s="11" t="n"/>
+      <c r="E18" s="11" t="n"/>
+      <c r="F18" s="11" t="n"/>
+      <c r="G18" s="11" t="n"/>
       <c r="H18" s="11" t="n"/>
       <c r="I18" s="11" t="n"/>
       <c r="J18" s="11" t="n"/>
       <c r="K18" s="11" t="n"/>
       <c r="L18" s="11" t="n"/>
-      <c r="M18" s="11" t="inlineStr">
-        <is>
-          <t>Public - Online</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-11-25 15:23:27</t>
-        </is>
-      </c>
+      <c r="M18" s="11" t="n"/>
     </row>
     <row r="19" ht="15.75" customHeight="1" s="90">
       <c r="A19" s="10" t="n">
